--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104681_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104681_W25.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1488</v>
+        <v>5.7175</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2203</v>
+        <v>3.9156</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9285</v>
+        <v>1.802</v>
       </c>
       <c r="G2" t="n">
-        <v>0.194</v>
+        <v>0.1943</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3378</v>
+        <v>0.328</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1439</v>
+        <v>-0.1336</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0702</v>
+        <v>1.0518</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9028</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8762</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3444</v>
+        <v>0.907</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9648</v>
+        <v>0.6848</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3796</v>
+        <v>0.2221</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7959</v>
+        <v>2.7951</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8371</v>
+        <v>5.6015</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3845</v>
+        <v>5.0561</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4527</v>
+        <v>0.5454</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3333</v>
+        <v>4.3263</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2093</v>
+        <v>1.201</v>
       </c>
       <c r="I3" t="n">
-        <v>3.124</v>
+        <v>3.1253</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3086</v>
+        <v>4.2782</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9902</v>
+        <v>0.9718</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3185</v>
+        <v>3.3064</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0247</v>
+        <v>0.0481</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3846</v>
+        <v>1.1662</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2249</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1597</v>
+        <v>0.2211</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4423</v>
+        <v>5.0554</v>
       </c>
       <c r="E4" t="n">
-        <v>5.7573</v>
+        <v>5.4918</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.315</v>
+        <v>-0.4365</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1373</v>
+        <v>3.1395</v>
       </c>
       <c r="H4" t="n">
-        <v>3.609</v>
+        <v>3.5992</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4717</v>
+        <v>-0.4598</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3784</v>
+        <v>4.3533</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5948</v>
+        <v>3.5713</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2411</v>
+        <v>-1.2138</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1689</v>
+        <v>0.7793</v>
       </c>
       <c r="T4" t="n">
-        <v>0.738</v>
+        <v>0.506</v>
       </c>
       <c r="U4" t="n">
-        <v>0.431</v>
+        <v>0.2733</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8612</v>
+        <v>1.4747</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1061</v>
+        <v>-0.1201</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7551</v>
+        <v>1.5947</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1994</v>
+        <v>0.9263</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7461</v>
+        <v>-1.6571</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4532</v>
+        <v>2.5834</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6065</v>
+        <v>1.0927</v>
       </c>
       <c r="K5" t="n">
-        <v>1.527</v>
+        <v>-1.8863</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0795</v>
+        <v>2.9789</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4071</v>
+        <v>-0.1664</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6263</v>
+        <v>-0.3956</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.6293</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7014</v>
+        <v>0.3207</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8075</v>
+        <v>0.1531</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1062</v>
+        <v>0.1677</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8848</v>
+        <v>1.4086</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8064</v>
+        <v>-0.4095</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6912</v>
+        <v>1.8181</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9199000000000001</v>
+        <v>2.1975</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.655</v>
+        <v>1.7353</v>
       </c>
       <c r="I6" t="n">
-        <v>2.575</v>
+        <v>0.4622</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1111</v>
+        <v>2.5783</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.8742</v>
+        <v>1.5061</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9853</v>
+        <v>1.0722</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1912</v>
+        <v>-0.3808</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4104</v>
+        <v>-0.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-3.6421</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2619</v>
+        <v>0.2614</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5565</v>
+        <v>0.3388</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2946</v>
+        <v>-0.0774</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2265</v>
+        <v>-0.3487</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1977</v>
+        <v>0.4897</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0288</v>
+        <v>-0.8384</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.409</v>
+        <v>-0.4019</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6651</v>
+        <v>0.669</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0742</v>
+        <v>-1.0709</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2858</v>
+        <v>0.2671</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4778</v>
+        <v>0.4686</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6948</v>
+        <v>-0.669</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4733</v>
+        <v>0.3915</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4174</v>
+        <v>0.2925</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.056</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3778</v>
+        <v>-1.3052</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0419</v>
+        <v>-0.1277</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3358</v>
+        <v>-1.1775</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.1595</v>
+        <v>-3.1715</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6449</v>
+        <v>-2.6452</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5145</v>
+        <v>-0.5264</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.722</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6837</v>
+        <v>-1.6967</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9967</v>
+        <v>0.9747</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4725</v>
+        <v>-2.4496</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7156</v>
+        <v>0.7965</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6866</v>
+        <v>0.6429</v>
       </c>
       <c r="U8" t="n">
-        <v>0.029</v>
+        <v>0.1535</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9219</v>
+        <v>-2.24</v>
       </c>
       <c r="E9" t="n">
-        <v>0.643</v>
+        <v>-2.9405</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5649</v>
+        <v>0.7005</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9668</v>
+        <v>-4.3316</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4128</v>
+        <v>-2.7882</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.554</v>
+        <v>-1.5434</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7216</v>
+        <v>-2.8135</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3912</v>
+        <v>-1.7107</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3304</v>
+        <v>-1.1029</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6884</v>
+        <v>-1.518</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-1.0775</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8844</v>
+        <v>-0.4405</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>1.818</v>
+        <v>1.0916</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1897</v>
+        <v>0.4665</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3717</v>
+        <v>0.6251</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3413</v>
+        <v>-2.7351</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3296</v>
+        <v>-1.1009</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9883</v>
+        <v>-1.6342</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.3182</v>
+        <v>-0.5075</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7775</v>
+        <v>-0.1724</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5407</v>
+        <v>-0.3351</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7811</v>
+        <v>0.0372</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6908</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0903</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5371</v>
+        <v>-0.5447</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0867</v>
+        <v>-0.1724</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4504</v>
+        <v>-0.3724</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9769</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0393</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9376</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5463</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7359</v>
+        <v>-2.7391</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0968</v>
+        <v>-0.4876</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.639</v>
+        <v>-2.2516</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.509</v>
+        <v>-1.9617</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1732</v>
+        <v>-0.4081</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3359</v>
+        <v>-1.5537</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0373</v>
+        <v>0.7023</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.3825</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0373</v>
+        <v>0.3198</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5463</v>
+        <v>-2.664</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1732</v>
+        <v>-0.7906</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3732</v>
+        <v>-1.8734</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.995</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.0865</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0.0915</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3573</v>
+        <v>-3.3292</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6309</v>
+        <v>-2.7269</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7264</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.0488</v>
+        <v>-4.0549</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0793</v>
+        <v>-1.0799</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9694</v>
+        <v>-2.975</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3604</v>
+        <v>-1.3909</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1181</v>
+        <v>-0.1314</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2423</v>
+        <v>-1.2595</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.6884</v>
+        <v>-2.664</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1744</v>
+        <v>-0.1361</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0948</v>
+        <v>-0.1492</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0796</v>
+        <v>0.013</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.213500000000002</v>
+        <v>6.560399999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>7.007899999999998</v>
+        <v>7.039999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7941000000000004</v>
+        <v>-0.4797999999999994</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.627399999999999</v>
+        <v>-3.645199999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.175399999999998</v>
+        <v>-1.218399999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.452099999999999</v>
+        <v>-2.427</v>
       </c>
       <c r="J13" t="n">
-        <v>9.690999999999999</v>
+        <v>9.4345</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5351</v>
+        <v>2.377999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>7.1561</v>
+        <v>7.0562</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.3184</v>
+        <v>-13.0796</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.7101</v>
+        <v>-3.5965</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.6084</v>
+        <v>-9.4833</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.8783</v>
+        <v>-15.9342</v>
       </c>
       <c r="R13" t="n">
-        <v>17.0124</v>
+        <v>17.0724</v>
       </c>
       <c r="S13" t="n">
-        <v>6.2002</v>
+        <v>6.5731</v>
       </c>
       <c r="T13" t="n">
-        <v>4.582100000000001</v>
+        <v>4.967000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.618</v>
+        <v>1.606</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5067</v>
+        <v>2.4944</v>
       </c>
       <c r="W13" t="n">
-        <v>8.613</v>
+        <v>8.572899999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.1064</v>
+        <v>-6.0785</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8634</v>
+        <v>6.6897</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6623</v>
+        <v>3.9797</v>
       </c>
       <c r="F14" t="n">
-        <v>2.201</v>
+        <v>2.71</v>
       </c>
       <c r="G14" t="n">
-        <v>7.4391</v>
+        <v>7.4449</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5395</v>
+        <v>3.5466</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8997</v>
+        <v>3.8983</v>
       </c>
       <c r="J14" t="n">
-        <v>6.4357</v>
+        <v>6.4056</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5975</v>
+        <v>2.5855</v>
       </c>
       <c r="L14" t="n">
-        <v>3.8382</v>
+        <v>3.8201</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0034</v>
+        <v>1.0393</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9419</v>
+        <v>0.9611</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0614</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9387</v>
+        <v>-1.1194</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.868</v>
+        <v>-0.5138</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0707</v>
+        <v>-0.6056</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0282</v>
+        <v>2.4163</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0319</v>
+        <v>3.4785</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0037</v>
+        <v>-1.0622</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0806</v>
+        <v>0.0864</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6751</v>
+        <v>0.6886</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5945</v>
+        <v>-0.6021</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9131</v>
+        <v>1.8911</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2122</v>
+        <v>1.2066</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7009</v>
+        <v>0.6845</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8325</v>
+        <v>-1.8047</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5371</v>
+        <v>-0.518</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6403</v>
+        <v>-0.2636</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5202</v>
+        <v>-0.0468</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1201</v>
+        <v>-0.2168</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8148</v>
+        <v>1.8343</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1924</v>
+        <v>2.9194</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3776</v>
+        <v>-1.0851</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9458</v>
+        <v>2.9514</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1833</v>
+        <v>2.1746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7625</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0838</v>
+        <v>2.0556</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2255</v>
+        <v>1.1991</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8583</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.862</v>
+        <v>0.8958</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9578</v>
+        <v>0.9755</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0958</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8115</v>
+        <v>-0.8</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0575</v>
+        <v>-0.1769</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8689</v>
+        <v>-0.6231</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>K. KOSTADINOV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8407</v>
+        <v>0.4078</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1126</v>
+        <v>0.5039</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9533</v>
+        <v>-0.0961</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9941</v>
+        <v>-0.2751</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2958</v>
+        <v>0.0228</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6983</v>
+        <v>-0.2979</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.2347</v>
+        <v>0.6433</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6722</v>
+        <v>0.5688</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5625</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2406</v>
+        <v>-0.9184</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3764</v>
+        <v>-0.546</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1359</v>
+        <v>-0.3724</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0882</v>
+        <v>-0.4553</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1221</v>
+        <v>-0.1394</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0339</v>
+        <v>-0.3159</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. KOSTADINOV</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4021</v>
+        <v>-0.0643</v>
       </c>
       <c r="E18" t="n">
-        <v>0.507</v>
+        <v>-0.9499</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1048</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2784</v>
+        <v>-0.9867</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0202</v>
+        <v>-0.2958</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2985</v>
+        <v>-0.6909</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6461</v>
+        <v>-1.2492</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5715</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0746</v>
+        <v>-0.5662</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9245</v>
+        <v>0.2625</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5513</v>
+        <v>0.3871</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3732</v>
+        <v>-0.1246</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4537</v>
+        <v>0.1696</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1391</v>
+        <v>0.2993</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3145</v>
+        <v>-0.1297</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3043</v>
+        <v>-0.7444</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7021</v>
+        <v>-1.626</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3979</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4602</v>
+        <v>0.4677</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3262</v>
+        <v>-0.3219</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="J19" t="n">
-        <v>0.464</v>
+        <v>0.4338</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5754</v>
+        <v>-0.5935</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0395</v>
+        <v>1.0273</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0038</v>
+        <v>0.034</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2493</v>
+        <v>0.2716</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2531</v>
+        <v>-0.2377</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6964</v>
+        <v>-1.1439</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6049</v>
+        <v>-0.486</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0915</v>
+        <v>-0.6579</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MCKOY</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4653</v>
+        <v>-3.3674</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2308</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6961</v>
+        <v>-3.467</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2609</v>
+        <v>-1.6809</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2293</v>
+        <v>-0.8707</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0316</v>
+        <v>-0.8102</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2289</v>
+        <v>0.1834</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7486</v>
+        <v>0.0345</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.1489</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.032</v>
+        <v>-1.8643</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4807</v>
+        <v>-0.9052</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5513</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1832</v>
+        <v>-0.0327</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5939</v>
+        <v>-0.0838</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4107</v>
+        <v>0.0512</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1607</v>
+        <v>-2.3367</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6957</v>
+        <v>-3.607</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4865</v>
+        <v>-2.3166</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2092</v>
+        <v>-1.2905</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8594</v>
+        <v>1.8536</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9479</v>
+        <v>0.956</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9115</v>
+        <v>0.8976</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9959</v>
+        <v>2.954</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5168</v>
+        <v>1.5029</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4791</v>
+        <v>1.4511</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1365</v>
+        <v>-1.1004</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5689</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8331</v>
+        <v>-1.729</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9043</v>
+        <v>-0.6692</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9288</v>
+        <v>-1.0598</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>J. MCKOY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9877</v>
+        <v>-3.8259</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3726</v>
+        <v>-1.0911</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6151</v>
+        <v>-2.7348</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6919</v>
+        <v>-3.2638</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8789</v>
+        <v>-2.2315</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-1.0323</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1839</v>
+        <v>-0.2523</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0346</v>
+        <v>-0.7659</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1493</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8758</v>
+        <v>-3.0116</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9135</v>
+        <v>-1.4656</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-1.546</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6303</v>
+        <v>-0.1767</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5565</v>
+        <v>0.2993</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0738</v>
+        <v>-0.476</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.3461</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7098</v>
+        <v>-5.1613</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.1563</v>
+        <v>-4.5179</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5535</v>
+        <v>-0.6434</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9324</v>
+        <v>-2.9523</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4604</v>
+        <v>-2.4504</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.472</v>
+        <v>-0.5018</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0595</v>
+        <v>0.0144</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4515</v>
+        <v>-1.4586</v>
       </c>
       <c r="L23" t="n">
-        <v>1.511</v>
+        <v>1.473</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.992</v>
+        <v>-2.9667</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0089</v>
+        <v>-0.9918</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.9831</v>
+        <v>-1.9749</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4676</v>
+        <v>0.116</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7984</v>
+        <v>-0.0887</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3309</v>
+        <v>0.2047</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.2136</v>
+        <v>-5.422199999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7943000000000007</v>
+        <v>0.4795999999999996</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.0078</v>
+        <v>-5.9019</v>
       </c>
       <c r="G24" t="n">
-        <v>3.627400000000001</v>
+        <v>3.6452</v>
       </c>
       <c r="H24" t="n">
-        <v>1.175400000000001</v>
+        <v>1.2183</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4522</v>
+        <v>2.427</v>
       </c>
       <c r="J24" t="n">
-        <v>13.3184</v>
+        <v>13.0797</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7104</v>
+        <v>3.5964</v>
       </c>
       <c r="L24" t="n">
-        <v>9.6081</v>
+        <v>9.483200000000002</v>
       </c>
       <c r="M24" t="n">
-        <v>-9.691099999999999</v>
+        <v>-9.4345</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.535</v>
+        <v>-2.3782</v>
       </c>
       <c r="O24" t="n">
-        <v>-7.156200000000001</v>
+        <v>-7.0564</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.134199999999999</v>
+        <v>-1.138099999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-17.0125</v>
+        <v>-17.0725</v>
       </c>
       <c r="R24" t="n">
-        <v>15.8783</v>
+        <v>15.9342</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.2002</v>
+        <v>-5.435</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.6179</v>
+        <v>-1.606</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.582000000000001</v>
+        <v>-3.8289</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.5067</v>
+        <v>-2.4944</v>
       </c>
       <c r="W24" t="n">
-        <v>6.1063</v>
+        <v>6.0784</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.613000000000001</v>
+        <v>-8.573</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104681_W25.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104681_W25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.0785</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104681_W25.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-8.573</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
